--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\XYRogueLike_ET\XYRogueLike_ET\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169B8F0E-46A8-469F-B273-65AAB883C959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC437AC0-02E7-45A0-A9D9-0F89DCFF5D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4104" yWindow="2724" windowWidth="23040" windowHeight="12672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -118,6 +118,10 @@
   </si>
   <si>
     <t>公共职能服</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏三区</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -511,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:H10"/>
+  <dimension ref="C2:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -669,6 +673,26 @@
         <v>17</v>
       </c>
     </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
